--- a/sources/table_normalization/xlsx/economy-table43.xlsx
+++ b/sources/table_normalization/xlsx/economy-table43.xlsx
@@ -193,13 +193,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -532,31 +532,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -566,6 +557,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -889,42 +889,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="22"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="21" t="s">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="19"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="22"/>
-      <c r="H1" s="23"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="38" customHeight="1" thickTop="1">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="15" t="s">
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="14" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1891,25 +1891,25 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14">
+      <c r="B40" s="21"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22">
         <f>SUM(D3:D39)</f>
         <v>42</v>
       </c>
-      <c r="E40" s="14">
+      <c r="E40" s="22">
         <f>SUM(E3:E39)</f>
         <v>25</v>
       </c>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14">
+      <c r="F40" s="22"/>
+      <c r="G40" s="22">
         <f>SUM(G3:G39)</f>
         <v>42</v>
       </c>
-      <c r="H40" s="14">
+      <c r="H40" s="22">
         <v>18</v>
       </c>
     </row>
